--- a/Assets/StreamingAssets/Levels/Levels.xlsx
+++ b/Assets/StreamingAssets/Levels/Levels.xlsx
@@ -6,14 +6,14 @@
     <workbookView tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Level1" sheetId="5" r:id="rId4"/>
-    <sheet name="Level2" sheetId="6" r:id="rId5"/>
+    <sheet name="Level1" sheetId="1" r:id="rId3"/>
+    <sheet name="Level2" sheetId="2" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="19">
   <si>
     <t xml:space="preserve">Distance</t>
   </si>
@@ -30,34 +30,22 @@
     <t xml:space="preserve">Gate</t>
   </si>
   <si>
-    <t xml:space="preserve">+5</t>
-  </si>
-  <si>
     <t xml:space="preserve">x2</t>
   </si>
   <si>
-    <t xml:space="preserve">+10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3</t>
-  </si>
-  <si>
     <t xml:space="preserve">x3</t>
   </si>
   <si>
-    <t xml:space="preserve">+20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Obstacle</t>
   </si>
   <si>
     <t xml:space="preserve">Saw</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+15</t>
+    <t xml:space="preserve">Hole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left</t>
   </si>
   <si>
     <t xml:space="preserve">÷2</t>
@@ -69,49 +57,19 @@
     <t xml:space="preserve">Flame</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+30</t>
-  </si>
-  <si>
     <t xml:space="preserve">÷3</t>
   </si>
   <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
     <t xml:space="preserve">x4</t>
   </si>
   <si>
-    <t xml:space="preserve">+100</t>
+    <t xml:space="preserve">Boss</t>
   </si>
   <si>
     <t xml:space="preserve">x5</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
     <t xml:space="preserve">x10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+200</t>
   </si>
 </sst>
 </file>
@@ -154,9 +112,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -180,11 +138,11 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -194,11 +152,11 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>-3</v>
       </c>
     </row>
     <row r="4">
@@ -209,10 +167,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -220,167 +178,195 @@
         <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>-10</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>25</v>
+      </c>
+      <c r="D15">
+        <v>-5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
+        <v>470</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
         <v>510</v>
       </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>560</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -388,9 +374,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -414,11 +400,11 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
+      <c r="C2">
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -428,11 +414,11 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
+      <c r="C3">
+        <v>-5</v>
+      </c>
+      <c r="D3">
+        <v>-5</v>
       </c>
     </row>
     <row r="4">
@@ -440,167 +426,195 @@
         <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
         <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>26</v>
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
+        <v>460</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
         <v>500</v>
       </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>550</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17">
+        <v>50</v>
+      </c>
+      <c r="D17">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Levels/Levels.xlsx
+++ b/Assets/StreamingAssets/Levels/Levels.xlsx
@@ -1,19 +1,35 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr autoCompressPictures="1"/>
-  <bookViews>
-    <workbookView tabRatio="600"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Level1" sheetId="1" r:id="rId3"/>
-    <sheet name="Level2" sheetId="2" r:id="rId4"/>
-  </sheets>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes" xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <ScaleCrop>false</ScaleCrop>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <Application>NPOI</Application>
+  <DocSecurity>0</DocSecurity>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="19">
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-05-06T08:54:47Z</dcterms:created>
+  <dc:creator>NPOI</dc:creator>
+</coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties">
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="Generator">
+    <lpwstr xmlns="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">NPOI</lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="Generator Version">
+    <lpwstr xmlns="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">2.8.0</lpwstr>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="29">
   <si>
     <t xml:space="preserve">Distance</t>
   </si>
@@ -70,11 +86,41 @@
   </si>
   <si>
     <t xml:space="preserve">x10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finish</t>
   </si>
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
   <fonts count="1">
@@ -112,7 +158,20 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr autoCompressPictures="1"/>
+  <bookViews>
+    <workbookView tabRatio="600"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Level1" sheetId="1" r:id="rId3"/>
+    <sheet name="Level2" sheetId="2" r:id="rId4"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
@@ -138,8 +197,8 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>5</v>
+      <c r="C2" t="s">
+        <v>19</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -152,8 +211,8 @@
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>10</v>
+      <c r="C3" t="s">
+        <v>20</v>
       </c>
       <c r="D3">
         <v>-3</v>
@@ -169,8 +228,8 @@
       <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4">
-        <v>20</v>
+      <c r="D4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -208,8 +267,8 @@
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7">
-        <v>15</v>
+      <c r="C7" t="s">
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -264,8 +323,8 @@
       <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="C11">
-        <v>30</v>
+      <c r="C11" t="s">
+        <v>23</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -295,8 +354,8 @@
       <c r="C13" t="s">
         <v>5</v>
       </c>
-      <c r="D13">
-        <v>50</v>
+      <c r="D13" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -320,7 +379,7 @@
       <c r="B15" t="s">
         <v>4</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="s">
         <v>25</v>
       </c>
       <c r="D15">
@@ -351,8 +410,8 @@
       <c r="C17" t="s">
         <v>15</v>
       </c>
-      <c r="D17">
-        <v>100</v>
+      <c r="D17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -360,13 +419,7 @@
         <v>560</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18">
-        <v>30</v>
-      </c>
-      <c r="D18">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -374,7 +427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
@@ -400,8 +453,8 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>10</v>
+      <c r="C2" t="s">
+        <v>20</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -473,8 +526,8 @@
       <c r="C7" t="s">
         <v>6</v>
       </c>
-      <c r="D7">
-        <v>30</v>
+      <c r="D7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -512,8 +565,8 @@
       <c r="B10" t="s">
         <v>4</v>
       </c>
-      <c r="C10">
-        <v>50</v>
+      <c r="C10" t="s">
+        <v>24</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -557,8 +610,8 @@
       <c r="C13" t="s">
         <v>17</v>
       </c>
-      <c r="D13">
-        <v>100</v>
+      <c r="D13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -599,8 +652,8 @@
       <c r="C16" t="s">
         <v>18</v>
       </c>
-      <c r="D16">
-        <v>200</v>
+      <c r="D16" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -612,9 +665,6 @@
       </c>
       <c r="C17">
         <v>50</v>
-      </c>
-      <c r="D17">
-        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Levels/Levels.xlsx
+++ b/Assets/StreamingAssets/Levels/Levels.xlsx
@@ -1,35 +1,19 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes" xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
-  <ScaleCrop>false</ScaleCrop>
-  <LinksUpToDate>false</LinksUpToDate>
-  <SharedDoc>false</SharedDoc>
-  <HyperlinksChanged>false</HyperlinksChanged>
-  <Application>NPOI</Application>
-  <DocSecurity>0</DocSecurity>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr autoCompressPictures="1"/>
+  <bookViews>
+    <workbookView tabRatio="600"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Level1" sheetId="1" r:id="rId3"/>
+    <sheet name="Level2" sheetId="2" r:id="rId4"/>
+  </sheets>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-05-06T08:54:47Z</dcterms:created>
-  <dc:creator>NPOI</dc:creator>
-</coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="Generator">
-    <lpwstr xmlns="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">NPOI</lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="Generator Version">
-    <lpwstr xmlns="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">2.8.0</lpwstr>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="29">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="39">
   <si>
     <t xml:space="preserve">Distance</t>
   </si>
@@ -116,11 +100,41 @@
   </si>
   <si>
     <t xml:space="preserve">Finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obstacle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spinner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">center,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left,2</t>
   </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
   <fonts count="1">
@@ -158,22 +172,9 @@
 </styleSheet>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr autoCompressPictures="1"/>
-  <bookViews>
-    <workbookView tabRatio="600"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Level1" sheetId="1" r:id="rId3"/>
-    <sheet name="Level2" sheetId="2" r:id="rId4"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,12 +423,152 @@
         <v>28</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>90</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>150</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>185</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>260</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>330</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>370</v>
+      </c>
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>450</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>490</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>

--- a/Assets/StreamingAssets/Levels/Levels.xlsx
+++ b/Assets/StreamingAssets/Levels/Levels.xlsx
@@ -1,148 +1,156 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr autoCompressPictures="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Unity\SnowmanCount\Assets\StreamingAssets\Levels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E39622-E709-4362-AB00-F1FA6DAD9E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView tabRatio="600"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Level1" sheetId="1" r:id="rId3"/>
-    <sheet name="Level2" sheetId="2" r:id="rId4"/>
+    <sheet name="Level1" sheetId="1" r:id="rId1"/>
+    <sheet name="Level2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="39">
-  <si>
-    <t xml:space="preserve">Distance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ObjectType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SubValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obstacle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">÷2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enemy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">÷3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obstacle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">saw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left,1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spinner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">right,2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">center,1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">left,2</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="37">
+  <si>
+    <t>Distance</t>
+  </si>
+  <si>
+    <t>ObjectType</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>SubValue</t>
+  </si>
+  <si>
+    <t>Gate</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>Obstacle</t>
+  </si>
+  <si>
+    <t>Saw</t>
+  </si>
+  <si>
+    <t>Hole</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>÷2</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>Flame</t>
+  </si>
+  <si>
+    <t>÷3</t>
+  </si>
+  <si>
+    <t>x4</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>x5</t>
+  </si>
+  <si>
+    <t>x10</t>
+  </si>
+  <si>
+    <t>+10</t>
+  </si>
+  <si>
+    <t>+20</t>
+  </si>
+  <si>
+    <t>+15</t>
+  </si>
+  <si>
+    <t>+30</t>
+  </si>
+  <si>
+    <t>+50</t>
+  </si>
+  <si>
+    <t>+100</t>
+  </si>
+  <si>
+    <t>+200</t>
+  </si>
+  <si>
+    <t>Finish</t>
+  </si>
+  <si>
+    <t>obstacle</t>
+  </si>
+  <si>
+    <t>saw</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>wall</t>
+  </si>
+  <si>
+    <t>left,1</t>
+  </si>
+  <si>
+    <t>spinner</t>
+  </si>
+  <si>
+    <t>right,2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>center,1</t>
+  </si>
+  <si>
+    <t>left,2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -151,7 +159,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -164,20 +172,332 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -191,35 +511,35 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>19</v>
+      <c r="C2">
+        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>40</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>20</v>
+      <c r="C3">
+        <v>70</v>
       </c>
       <c r="D3">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>75</v>
       </c>
@@ -230,10 +550,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>110</v>
       </c>
@@ -247,7 +567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>115</v>
       </c>
@@ -261,7 +581,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>130</v>
       </c>
@@ -269,13 +589,13 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>170</v>
       </c>
@@ -286,10 +606,10 @@
         <v>13</v>
       </c>
       <c r="D8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>200</v>
       </c>
@@ -303,7 +623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>240</v>
       </c>
@@ -317,21 +637,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>270</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="C11" t="s">
-        <v>23</v>
+      <c r="C11">
+        <v>60</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>310</v>
       </c>
@@ -342,10 +662,10 @@
         <v>13</v>
       </c>
       <c r="D12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>350</v>
       </c>
@@ -356,10 +676,10 @@
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>390</v>
       </c>
@@ -373,21 +693,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>430</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
-      <c r="C15" t="s">
-        <v>25</v>
+      <c r="C15">
+        <v>40</v>
       </c>
       <c r="D15">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>470</v>
       </c>
@@ -398,10 +718,10 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>510</v>
       </c>
@@ -412,168 +732,169 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>560</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
         <v>29</v>
       </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>90</v>
       </c>
       <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
         <v>29</v>
       </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>150</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>185</v>
       </c>
       <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
         <v>29</v>
       </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>260</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
         <v>34</v>
       </c>
-      <c r="D24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>330</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>370</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>450</v>
       </c>
       <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
         <v>29</v>
       </c>
-      <c r="C27" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>490</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.375" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -587,7 +908,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -595,13 +916,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>50</v>
       </c>
@@ -615,7 +936,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>90</v>
       </c>
@@ -629,7 +950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>95</v>
       </c>
@@ -643,7 +964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>120</v>
       </c>
@@ -657,7 +978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>150</v>
       </c>
@@ -668,10 +989,10 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>190</v>
       </c>
@@ -685,7 +1006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>220</v>
       </c>
@@ -699,7 +1020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>260</v>
       </c>
@@ -707,13 +1028,13 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>300</v>
       </c>
@@ -727,7 +1048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>340</v>
       </c>
@@ -741,7 +1062,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>380</v>
       </c>
@@ -752,10 +1073,10 @@
         <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>420</v>
       </c>
@@ -769,7 +1090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>460</v>
       </c>
@@ -783,7 +1104,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>500</v>
       </c>
@@ -794,10 +1115,10 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>550</v>
       </c>
@@ -809,6 +1130,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>